--- a/docs/reports/briefings/business/2026-08-17-国际业务部方案任务开场表.xlsx
+++ b/docs/reports/briefings/business/2026-08-17-国际业务部方案任务开场表.xlsx
@@ -9,9 +9,14 @@
   <sheets>
     <sheet name="开场表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="丢单原因分类" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="重点按人" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="重点明细" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'开场表'!$A$3:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'重点按人'!$A$3:$F$15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'重点按人'!3:3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'重点明细'!$A$3:$F$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +64,24 @@
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -82,8 +103,18 @@
         <fgColor rgb="00C00000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -105,11 +136,25 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -136,6 +181,42 @@
     </xf>
     <xf numFmtId="9" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1118,4 +1199,964 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>重点项目按业务员（截至 2026-08-17）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>15 条重点（标题标注 + 补录生力取料机、MAK 2×150）。按开场表组别、业务员排。张硕/马鹏飞/韩鸿彪/尹韬越为 0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>组别</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>重点</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>已签约</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>进行中有效</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>该降级 / 已暂停</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>一组</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>一组</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>二组</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>二组</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>王伟超</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>三组</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>1 浅层</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>三组</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>五组</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>1 前期</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>五组</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>六组</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>六组</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>1 已暂停</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>俄语组</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>1 浅层</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>俄语组</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>陈子凡 4 条全有效（含唯一签约）。该降级 4 条：王伟乐 CIMAF 浅层、陈辉塞拉利昂前期、苗恒孟加拉已暂停、崔阳 75 万吨浅层。韩鸿彪未标重点，但有效项目率全员最高。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:F15"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A18:F18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>重点项目明细 15 条（按业务员）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>按开场表组别、业务员排列。补录 2 条：陈子凡生力取料机、MAK 2×150 吨（已签约）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>组别</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>判断</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>一句话</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>一组</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>蒙古 MAK 2×150 吨小仓</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>已结项-签约</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>已签约</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>样本内唯一签约</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>一组</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>蒙古 MAK 气力输送更新</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>进行中（近期可成交）</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>最接近成单的在手重点</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>一组</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>菲律宾生力取料机</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>等授标</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>一组</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>MONCEMENT 3×2000 水泥中转</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>拜访后更新方案</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>二组</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>斯里兰卡 30×3500 稻谷</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>已到决策期，钢构单价拿不到</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>二组</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>王伟超</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>哥斯达黎加咖啡仓</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>到过工厂，多次改图</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>三组</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>新加坡裕廊港 12×10000</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>最新价澄清中</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>三组</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>摩洛哥 CIMAF 1×700</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>浅层</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>已报价、库龄偏长</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>五组</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>韩国大宇 3 万吨磷矿粉</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>多次报价，比仓型</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>五组</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>Lanwa 水泥混拌</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>老客户，利润被压</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>五组</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>塞拉利昂 2×3 万吨 clinker</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>已拜访，缺资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>五组</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>坦桑 2×4500 小麦仓</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>曾接受报价，新要求已反馈</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>六组</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>墨西哥大型粮仓</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>V4 后更报价 V2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>六组</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>孟加拉 2×3000 稻谷</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>暂停</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>已暂停</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>重点已暂停，处理正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>俄语组</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>75 万吨小麦深加工</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>浅层</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>只写「进行中 重点任务」，无下一步</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>15 = 已签约 1 + 进行中有效 10 + 该降级/已暂停 4（CIMAF 浅层、塞拉利昂前期、孟加拉暂停、崔阳 75 万吨浅层）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:F18"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A20:F20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/docs/reports/briefings/business/2026-08-17-国际业务部方案任务开场表.xlsx
+++ b/docs/reports/briefings/business/2026-08-17-国际业务部方案任务开场表.xlsx
@@ -11,12 +11,16 @@
     <sheet name="丢单原因分类" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="重点按人" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="重点明细" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="客户集中度排名" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="多项目客户" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'开场表'!$A$3:$G$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'重点按人'!$A$3:$F$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'重点按人'!3:3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'重点明细'!$A$3:$F$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'客户集中度排名'!$A$3:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'多项目客户'!$A$3:$K$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -81,7 +85,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -111,6 +115,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -154,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -218,6 +237,37 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="8" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2159,4 +2209,1020 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>客户集中度排名（截至 2026-08-17）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>条/客 = 任务 ÷ 客户。全员 1.23。高不一定好：拆单和基本盘都会抬高。张硕、王伟超并列 11。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>组别</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>任务</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>条/客</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>最大客户</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>怎么读</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>俄语组</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="F4" s="23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>拆单注水</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>Powerz ×7</t>
+        </is>
+      </c>
+      <c r="I4" s="20" t="inlineStr">
+        <is>
+          <t>前三户 16 条，集中在死单</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>六组</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>基本盘深挖</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>QNC ×4</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>占本人 36%，健康但单一</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>一组</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>基本盘深挖</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>生力 ×4</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>生力 + MAK，含唯一签约</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>五组</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G7" s="27" t="inlineStr">
+        <is>
+          <t>渠道多询</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>Kim ×4</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>一个渠道四条询价，关了 3 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>五组</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>样本小</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>C00009344 ×2</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>同一编码跨土库曼 / 新疆</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>二组</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>局部拆单</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>咖啡仓 ×3</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>面上不集中，三条全挂着</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>俄语组</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" s="26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>接近一人一客</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>征地 V1/V2 ×2</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>只多拆了征地</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>六组</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>广撒网</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>铺得最开，留下 5 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>三组</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="F12" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>广撒网</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>11 条死 7 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>三组</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>广撒网</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>一半丢掉</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>一组</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>广撒网</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>样本小；斯里兰卡跟得细</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>二组</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>王伟超</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>广撒网</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>样本小；哥斯达黎加到过工厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="18" t="inlineStr"/>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n">
+        <v>165</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>134</v>
+      </c>
+      <c r="F16" s="31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="18" t="n"/>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>崔阳最高是拆单；韩鸿彪、陈子凡是基本盘。底下五个 1.00 是一人一客、铺新客户。冯乐/张硕/王伟超样本小于 8。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:I15"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A18:I18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>项目数大于 2 的客户（截至 2026-08-17）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>项目数 &gt; 2 的客户 7 户、31 条。刚好 2 条的不进本榜（含蒙古 MAK）。生力/SMC/Manila01 已并户。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>编码</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>项目数</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>已丢</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>暂停</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>有效在手</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>怎么读</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>Powerz</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>C00006570</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="24" t="inlineStr">
+        <is>
+          <t>拆单注水</t>
+        </is>
+      </c>
+      <c r="K4" s="20" t="inlineStr">
+        <is>
+          <t>5 条已丢给当地/其他供应商；底渣机该停未停</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>Эннова</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>C00007843</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="24" t="inlineStr">
+        <is>
+          <t>拆单注水</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>3 条方案未出数月仍写希望不大</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>菲律宾生力集团</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>无编码，已并户</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>基本盘深挖</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>临建、平方仓已丢；取料机等授标</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>韩国 Kim</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>C00001305</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="27" t="inlineStr">
+        <is>
+          <t>渠道多询</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>一个渠道四条询价，关掉 3 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>cotes</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>C00006514</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="27" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>两处技术探讨还在；装配仓已丢</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>越南 QNC</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>C00008036</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>基本盘深挖</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>料场/船对船已暂停；输送还在跟</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>咖啡仓</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>C00008345</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="24" t="inlineStr">
+        <is>
+          <t>拆单注水</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>方仓、缓冲斗、Probat 三条全挂着</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>崔阳 Powerz + Эннова + cotes = 16 条。生力、QNC 是基本盘；Powerz、Эннова、咖啡仓是拆单。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:K10"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A12:K12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/docs/reports/briefings/business/2026-08-17-国际业务部方案任务开场表.xlsx
+++ b/docs/reports/briefings/business/2026-08-17-国际业务部方案任务开场表.xlsx
@@ -16,9 +16,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'开场表'!$A$3:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'重点按人'!$A$3:$F$15</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'重点按人'!3:3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'重点明细'!$A$3:$F$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'重点按人'!$A$3:$E$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'重点明细'!$A$3:$G$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'客户集中度排名'!$A$3:$I$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'多项目客户'!$A$3:$K$10</definedName>
   </definedNames>
@@ -1255,17 +1254,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1275,10 +1273,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>15 条重点（标题标注 + 补录生力取料机、MAK 2×150）。按开场表组别、业务员排。张硕/马鹏飞/韩鸿彪/尹韬越为 0。</t>
+          <t>按任务标题「重点项目」13 条（已剔郭朝伟）+ 补录菲律宾生力取料机。MAK 2×150 已签约但标题未标，不进本清单。合计 14。</t>
         </is>
       </c>
     </row>
@@ -1300,15 +1298,10 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>已签约</t>
+          <t>进行中有效</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>进行中有效</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>该降级 / 已暂停</t>
         </is>
@@ -1326,15 +1319,12 @@
         </is>
       </c>
       <c r="C4" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1358,9 +1348,6 @@
       <c r="E5" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
@@ -1377,12 +1364,9 @@
         <v>1</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1401,12 +1385,9 @@
         <v>1</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1425,12 +1406,9 @@
         <v>2</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>1 浅层</t>
         </is>
@@ -1456,9 +1434,6 @@
       <c r="E9" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
@@ -1475,12 +1450,9 @@
         <v>3</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>1 前期</t>
         </is>
@@ -1501,12 +1473,9 @@
         <v>1</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1530,9 +1499,6 @@
       <c r="E12" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
@@ -1549,12 +1515,9 @@
         <v>2</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>1 已暂停</t>
         </is>
@@ -1577,10 +1540,7 @@
       <c r="D14" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>1 浅层</t>
         </is>
@@ -1606,11 +1566,8 @@
       <c r="E15" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
+    </row>
+    <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
           <t>合计</t>
@@ -1618,34 +1575,30 @@
       </c>
       <c r="B16" s="18" t="n"/>
       <c r="C16" s="18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="18" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>陈子凡 4 条全有效（含唯一签约）。该降级 4 条：王伟乐 CIMAF 浅层、陈辉塞拉利昂前期、苗恒孟加拉已暂停、崔阳 75 万吨浅层。韩鸿彪未标重点，但有效项目率全员最高。</t>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>14 = 进行中有效 10 + 该降级/已暂停 4。生力取料机为补录。唯一签约 MAK 2×150 不在本清单。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F15"/>
+  <autoFilter ref="A3:E15"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1653,30 +1606,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>重点项目明细 15 条（按业务员）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
+          <t>重点项目明细 14 条（按业务员）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>按开场表组别、业务员排列。补录 2 条：陈子凡生力取料机、MAK 2×150 吨（已签约）。</t>
+          <t>按任务标题「重点项目」13 条（已剔郭朝伟）+ 补录菲律宾生力取料机。MAK 2×150 已签约但标题未标，不进本清单。合计 14。</t>
         </is>
       </c>
     </row>
@@ -1698,15 +1652,20 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>判断</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>一句话</t>
         </is>
@@ -1725,22 +1684,27 @@
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>蒙古 MAK 2×150 吨小仓</t>
+          <t>蒙古 MAK 气力输送更新</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>已结项-签约</t>
-        </is>
-      </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>已签约</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="inlineStr">
-        <is>
-          <t>样本内唯一签约</t>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>进行中（近期可成交）</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>标题重点；最接近成单</t>
         </is>
       </c>
     </row>
@@ -1757,22 +1721,27 @@
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>蒙古 MAK 气力输送更新</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>进行中（近期可成交）</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
+          <t>菲律宾生力取料机</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>补录</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>有效</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>最接近成单的在手重点</t>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>补录，标题未写重点；等授标</t>
         </is>
       </c>
     </row>
@@ -1789,54 +1758,64 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>菲律宾生力取料机</t>
+          <t>MONCEMENT 3×2000 水泥中转</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>有效</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
-        <is>
-          <t>等授标</t>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>拜访后更新方案</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>一组</t>
+          <t>二组</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>陈子凡</t>
+          <t>司斌</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>MONCEMENT 3×2000 水泥中转</t>
+          <t>斯里兰卡 30×3500 稻谷</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>有效</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>拜访后更新方案</t>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>已到决策期，钢构单价拿不到</t>
         </is>
       </c>
     </row>
@@ -1848,59 +1827,69 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>司斌</t>
+          <t>王伟超</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>斯里兰卡 30×3500 稻谷</t>
+          <t>哥斯达黎加咖啡仓</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>有效</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>已到决策期，钢构单价拿不到</t>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>到过工厂，多次改图</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>二组</t>
+          <t>三组</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>王伟超</t>
+          <t>王伟乐</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>哥斯达黎加咖啡仓</t>
+          <t>新加坡裕廊港 12×10000</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>有效</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>到过工厂，多次改图</t>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>最新价澄清中</t>
         </is>
       </c>
     </row>
@@ -1917,54 +1906,64 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>新加坡裕廊港 12×10000</t>
+          <t>摩洛哥 CIMAF 1×700</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>最新价澄清中</t>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>浅层</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>已报价、库龄偏长</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>三组</t>
+          <t>五组</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>王伟乐</t>
+          <t>陈辉</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>摩洛哥 CIMAF 1×700</t>
+          <t>韩国大宇 3 万吨磷矿粉</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>浅层</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>已报价、库龄偏长</t>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>多次报价，比仓型</t>
         </is>
       </c>
     </row>
@@ -1981,22 +1980,27 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>韩国大宇 3 万吨磷矿粉</t>
+          <t>Lanwa 水泥混拌</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>有效</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
-        <is>
-          <t>多次报价，比仓型</t>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>老客户，利润被压</t>
         </is>
       </c>
     </row>
@@ -2013,22 +2017,27 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>Lanwa 水泥混拌</t>
+          <t>塞拉利昂 2×3 万吨 clinker</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>老客户，利润被压</t>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>已拜访，缺资金</t>
         </is>
       </c>
     </row>
@@ -2040,59 +2049,69 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>陈辉</t>
+          <t>冯乐</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>塞拉利昂 2×3 万吨 clinker</t>
+          <t>坦桑 2×4500 小麦仓</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>前期</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>已拜访，缺资金</t>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>曾接受报价，新要求已反馈</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>五组</t>
+          <t>六组</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>冯乐</t>
+          <t>苗恒</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>坦桑 2×4500 小麦仓</t>
+          <t>墨西哥大型粮仓</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>有效</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>曾接受报价，新要求已反馈</t>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>V4 后更报价 V2</t>
         </is>
       </c>
     </row>
@@ -2109,105 +2128,82 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>墨西哥大型粮仓</t>
+          <t>孟加拉 2×3000 稻谷</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>V4 后更报价 V2</t>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>暂停</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>已暂停</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>重点已暂停，处理正确</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>六组</t>
+          <t>俄语组</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>苗恒</t>
+          <t>崔阳</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>孟加拉 2×3000 稻谷</t>
+          <t>75 万吨小麦深加工</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>暂停</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>已暂停</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>重点已暂停，处理正确</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>俄语组</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>崔阳</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>75 万吨小麦深加工</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>浅层</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>只写「进行中 重点任务」，无下一步</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="22" t="inlineStr">
-        <is>
-          <t>15 = 已签约 1 + 进行中有效 10 + 该降级/已暂停 4（CIMAF 浅层、塞拉利昂前期、孟加拉暂停、崔阳 75 万吨浅层）。</t>
+    <row r="19">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>14 = 进行中有效 10 + 该降级/已暂停 4。生力取料机为补录。唯一签约 MAK 2×150 不在本清单。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F18"/>
+  <autoFilter ref="A3:G17"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:G19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 

--- a/docs/reports/briefings/business/2026-08-17-国际业务部方案任务开场表.xlsx
+++ b/docs/reports/briefings/business/2026-08-17-国际业务部方案任务开场表.xlsx
@@ -9,17 +9,18 @@
   <sheets>
     <sheet name="开场表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="丢单原因分类" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="重点按人" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="重点明细" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="客户集中度排名" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="多项目客户" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="丢单含暂停77" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="重点按人" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="重点明细" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="客户集中度排名" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="多项目客户" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'开场表'!$A$3:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'重点按人'!$A$3:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'重点明细'!$A$3:$G$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'客户集中度排名'!$A$3:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'多项目客户'!$A$3:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'重点按人'!$A$3:$E$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'重点明细'!$A$3:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'客户集中度排名'!$A$3:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'多项目客户'!$A$3:$K$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +85,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -131,6 +132,26 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2D5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F9FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAF8"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -172,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -267,6 +288,63 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1254,6 +1332,183 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>已丢单（含暂停）77 条：原因分类（截至 2026-08-17）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="34" t="inlineStr">
+        <is>
+          <t>77 = 已关掉判定丢掉 60 + 暂停 17。暂停按进展并入同一五类：失联5、改计划10、价格1、选其他1。一条只归一类。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>原因分类</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>条数</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>主要是谁</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>失联 / 报后无反馈</t>
+        </is>
+      </c>
+      <c r="B4" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="C4" s="36" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="D4" s="37" t="inlineStr">
+        <is>
+          <t>尹韬越6、苗恒5、马鹏飞4、王伟乐4、司斌4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>需求不实 / 未立项 / 改计划</t>
+        </is>
+      </c>
+      <c r="B5" s="38" t="n">
+        <v>18</v>
+      </c>
+      <c r="C5" s="39" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="D5" s="40" t="inlineStr">
+        <is>
+          <t>苗恒5、陈辉4、崔阳3、韩鸿彪2、陈子凡2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="41" t="inlineStr">
+        <is>
+          <t>价格 / 预算</t>
+        </is>
+      </c>
+      <c r="B6" s="41" t="n">
+        <v>13</v>
+      </c>
+      <c r="C6" s="42" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>崔阳5、尹韬越3、陈子凡2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="44" t="inlineStr">
+        <is>
+          <t>我方做不了 / 主动放弃</t>
+        </is>
+      </c>
+      <c r="B7" s="44" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" s="45" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="D7" s="46" t="inlineStr">
+        <is>
+          <t>陈子凡3、马鹏飞3、崔阳2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="47" t="inlineStr">
+        <is>
+          <t>选其他供应商 / 工艺</t>
+        </is>
+      </c>
+      <c r="B8" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" s="48" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="D8" s="49" t="inlineStr">
+        <is>
+          <t>崔阳7（Powerz为主）、苗恒1、韩鸿彪1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="50" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B9" s="50" t="n">
+        <v>77</v>
+      </c>
+      <c r="C9" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="52" t="inlineStr">
+        <is>
+          <t>已关60 + 暂停17</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>第一因仍是失联（28条，36%）。把暂停算进来后，第二因是项目自己停了（改计划18条，23%），不是价格打输。选其他家几乎全是崔阳Powerz。冯乐不在这77里——6条一笔没关。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A11:D11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E18"/>
@@ -1602,7 +1857,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2207,7 +2462,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2796,7 +3051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
